--- a/ボタンで遊べる電子工作品.xlsx
+++ b/ボタンで遊べる電子工作品.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Polaris Office Sheet" lastEdited="4" lowestEdited="4" rupBuild="10.115.186.54614"/>
+  <fileVersion appName="Polaris Office Sheet" lastEdited="4" lowestEdited="4" rupBuild="10.115.191.55897"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="570" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="560" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="SHEET1" sheetId="1" r:id="rId1"/>
@@ -1043,7 +1043,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B2:G13"/>
+  <dimension ref="B2:G14"/>
   <sheetFormatPr defaultRowHeight="13.200000" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="21.12999916" customWidth="1" outlineLevel="0"/>
@@ -1281,7 +1281,10 @@
       </c>
     </row>
     <row r="13" spans="2:7">
-      <c r="E13" s="0">
+      <c r="F13" s="1"/>
+    </row>
+    <row r="14" spans="2:7">
+      <c r="E14" s="0">
         <f>SUM(E3:E12)</f>
         <v>11980</v>
       </c>
